--- a/data/trans_dic/IP16A06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 10,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 11,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 8,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,91</t>
+          <t>0,71; 5,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,66</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 12,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,93</t>
+          <t>0,78; 7,17</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,25</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 11,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 9,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,83</t>
+          <t>1,27; 11,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,18</t>
+          <t>1,36; 7,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,48; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,88</t>
+          <t>0,43; 4,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,91</t>
+          <t>0,84; 5,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,56</t>
+          <t>0,37; 3,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,73</t>
+          <t>0,4; 3,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,64</t>
+          <t>0,91; 3,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,01</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,07</t>
+          <t>0,36; 2,03</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3119</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2774</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4900</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4003</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3137</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3591</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>590; 4831</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4724</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3480</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2640</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4375</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3149</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3983</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4668</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3438</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>515; 4752</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3677</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4151</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5719</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3588</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>635; 5715</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3274</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4815</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1373; 7991</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3278</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>600; 5792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>801; 7718</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1203; 7641</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>717; 7266</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>592; 5602</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2455; 9969</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2647; 10913</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6298</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Habitat-trans_dic.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,88</t>
+          <t>0,0; 9,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,77</t>
+          <t>0,0; 9,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,69</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,82</t>
+          <t>0,71; 6,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
     </row>
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,78</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,3</t>
+          <t>0,0; 12,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,17</t>
+          <t>0,78; 6,83</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,17</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,0; 11,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,24</t>
+          <t>0,0; 8,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,44</t>
+          <t>1,32; 11,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,93</t>
+          <t>1,35; 7,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,62</t>
+          <t>0,48; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,13</t>
+          <t>0,44; 4,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,31</t>
+          <t>0,85; 5,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,79</t>
+          <t>0,36; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,78</t>
+          <t>0,39; 3,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,7</t>
+          <t>0,91; 3,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,69; 2,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,36; 2,11</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3119</t>
+          <t>0; 2621</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2774</t>
+          <t>0; 3316</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1580,22 +1580,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4900</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4003</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3137</t>
+          <t>0; 3254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3591</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>590; 4831</t>
+          <t>592; 5030</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4724</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3480</t>
+          <t>0; 3100</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1753,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2640</t>
+          <t>0; 2164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>0; 2625</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3983</t>
+          <t>0; 4000</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4668</t>
+          <t>0; 4887</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 2825</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>515; 4752</t>
+          <t>520; 4528</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4151</t>
+          <t>0; 3201</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5719</t>
+          <t>0; 5625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,32 +1921,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 3457</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>635; 5715</t>
+          <t>660; 5496</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3274</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 4886</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1373; 7991</t>
+          <t>1360; 8038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3278</t>
+          <t>0; 3569</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>600; 5792</t>
+          <t>597; 5896</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>801; 7718</t>
+          <t>816; 7603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1203; 7641</t>
+          <t>1217; 7719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>717; 7266</t>
+          <t>691; 6602</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>592; 5602</t>
+          <t>584; 5067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2455; 9969</t>
+          <t>2461; 9327</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2647; 10913</t>
+          <t>2626; 11063</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1113; 6298</t>
+          <t>1107; 6564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,85</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,06</t>
+          <t>0,71; 5,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 11,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,35</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,83</t>
+          <t>0,79; 6,93</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,47</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,08</t>
+          <t>0,0; 10,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,91</t>
+          <t>0,0; 14,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,0</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,98</t>
+          <t>1,41; 8,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,7</t>
+          <t>0,82; 4,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,07</t>
+          <t>0,36; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,4; 3,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,36</t>
+          <t>0,48; 4,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,45</t>
+          <t>0,43; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,42</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,46</t>
+          <t>0,97; 3,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,92</t>
+          <t>0,7; 3,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,11</t>
+          <t>0,34; 2,07</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>553</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2323</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3316</t>
+          <t>0; 2290</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1252</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1331</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 3310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4035</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3254</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3224</t>
+          <t>0; 3869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4634</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>592; 5030</t>
+          <t>592; 4905</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4004</t>
+          <t>0; 4685</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3100</t>
+          <t>0; 3505</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2709</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2164</t>
+          <t>0; 3823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4116</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4000</t>
+          <t>0; 2555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 4724</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2825</t>
+          <t>0; 2555</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>520; 4528</t>
+          <t>522; 4595</t>
         </is>
       </c>
     </row>
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1617</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3201</t>
+          <t>0; 3472</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5625</t>
+          <t>0; 5408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3457</t>
+          <t>0; 3658</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>660; 5496</t>
+          <t>0; 4910</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4886</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1360; 8038</t>
+          <t>1420; 8243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3569</t>
+          <t>0; 3351</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>597; 5896</t>
+          <t>1184; 7061</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>816; 7603</t>
+          <t>689; 6824</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>589; 5531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1217; 7719</t>
+          <t>596; 5677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>691; 6602</t>
+          <t>798; 7263</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>584; 5067</t>
+          <t>0; 3951</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2461; 9327</t>
+          <t>2610; 9806</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2626; 11063</t>
+          <t>2631; 11380</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1107; 6564</t>
+          <t>1048; 6442</t>
         </is>
       </c>
     </row>
